--- a/data/trans_dic/POLIPATOLOGIA_5-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,85</t>
+          <t>1,58; 3,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,66</t>
+          <t>2,6; 5,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,92</t>
+          <t>2,84; 6,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,57</t>
+          <t>8,31; 12,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,54</t>
+          <t>2,56; 5,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,14</t>
+          <t>7,41; 12,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,74</t>
+          <t>8,76; 13,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,21; 19,27</t>
+          <t>13,58; 19,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,12</t>
+          <t>2,27; 4,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,3</t>
+          <t>5,53; 8,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 9,13</t>
+          <t>6,32; 9,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,91; 15,44</t>
+          <t>12,16; 15,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,09</t>
+          <t>2,62; 5,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,02</t>
+          <t>2,56; 5,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,46</t>
+          <t>2,12; 4,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,91</t>
+          <t>3,13; 8,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,57</t>
+          <t>4,38; 7,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,02</t>
+          <t>7,42; 11,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,07</t>
+          <t>7,19; 11,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 17,61</t>
+          <t>14,12; 17,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,94</t>
+          <t>3,93; 5,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,5</t>
+          <t>5,34; 7,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,14</t>
+          <t>4,96; 7,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,44</t>
+          <t>7,16; 12,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,09</t>
+          <t>2,21; 5,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,49</t>
+          <t>2,5; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,8</t>
+          <t>2,28; 4,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,44</t>
+          <t>5,78; 9,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,77</t>
+          <t>8,17; 12,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,47</t>
+          <t>7,32; 11,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,72</t>
+          <t>6,61; 10,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 62,35</t>
+          <t>13,4; 65,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,17</t>
+          <t>5,65; 8,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,18</t>
+          <t>5,44; 8,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,24</t>
+          <t>4,74; 7,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,42; 48,03</t>
+          <t>10,37; 46,83</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,15</t>
+          <t>2,62; 4,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,36</t>
+          <t>2,66; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,87</t>
+          <t>2,59; 5,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,26</t>
+          <t>6,91; 10,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,99</t>
+          <t>5,63; 8,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 13,28</t>
+          <t>9,23; 13,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,05</t>
+          <t>8,99; 13,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 19,22</t>
+          <t>13,79; 19,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,6</t>
+          <t>4,63; 6,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,09</t>
+          <t>6,63; 9,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,92</t>
+          <t>6,28; 8,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 14,69</t>
+          <t>11,17; 14,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,12</t>
+          <t>2,89; 4,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,49</t>
+          <t>3,12; 4,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,2</t>
+          <t>2,93; 4,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,95</t>
+          <t>6,21; 9,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,71</t>
+          <t>5,91; 7,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,91</t>
+          <t>8,9; 10,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75; 10,9</t>
+          <t>8,81; 11,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,76; 35,55</t>
+          <t>15,75; 35,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,69</t>
+          <t>4,57; 5,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 7,5</t>
+          <t>6,28; 7,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,33</t>
+          <t>6,1; 7,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 23,57</t>
+          <t>11,72; 22,67</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10492; 26731</t>
+          <t>10983; 26949</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18360; 39792</t>
+          <t>18258; 38315</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18440; 39916</t>
+          <t>19196; 40670</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52800; 79864</t>
+          <t>52785; 80637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17624; 38124</t>
+          <t>17633; 36692</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51709; 84621</t>
+          <t>51632; 85982</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59784; 92422</t>
+          <t>58928; 91318</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95823; 139748</t>
+          <t>98488; 140201</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31835; 57001</t>
+          <t>31384; 58582</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76654; 116246</t>
+          <t>77501; 114848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84986; 123056</t>
+          <t>85235; 124531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>162001; 210160</t>
+          <t>165495; 210951</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25371; 48933</t>
+          <t>25195; 48915</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25961; 51130</t>
+          <t>26110; 51383</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22816; 45631</t>
+          <t>21685; 43225</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43761; 106241</t>
+          <t>37347; 105847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43044; 73333</t>
+          <t>42426; 73661</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76122; 113798</t>
+          <t>76542; 114765</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74068; 115401</t>
+          <t>74995; 115818</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>134809; 168779</t>
+          <t>135388; 169226</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76078; 114686</t>
+          <t>75930; 113362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109395; 153666</t>
+          <t>109465; 155108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102229; 147503</t>
+          <t>102365; 149835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>150883; 267638</t>
+          <t>154073; 267467</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15340; 34562</t>
+          <t>14982; 36601</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19526; 41621</t>
+          <t>18971; 43022</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16201; 36473</t>
+          <t>17344; 36431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39780; 66513</t>
+          <t>40740; 67381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55739; 87312</t>
+          <t>55895; 85542</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56481; 89121</t>
+          <t>56906; 89810</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50998; 84146</t>
+          <t>51914; 83534</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>125265; 581982</t>
+          <t>125105; 611821</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76769; 111310</t>
+          <t>76927; 113882</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83217; 125588</t>
+          <t>83503; 126730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73444; 111891</t>
+          <t>73284; 112933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>170692; 786807</t>
+          <t>169896; 767159</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25644; 48497</t>
+          <t>24716; 45853</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25391; 50832</t>
+          <t>25217; 51777</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22306; 45652</t>
+          <t>24294; 48612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63651; 95053</t>
+          <t>64008; 94888</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60013; 93354</t>
+          <t>58436; 91814</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97292; 139707</t>
+          <t>97041; 140464</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93132; 136237</t>
+          <t>93884; 138405</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>149239; 210458</t>
+          <t>151024; 214421</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90836; 130639</t>
+          <t>91772; 129530</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132369; 181672</t>
+          <t>132547; 181960</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123545; 176733</t>
+          <t>124403; 175382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>234068; 297009</t>
+          <t>225749; 292210</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92695; 134837</t>
+          <t>94626; 136121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107465; 153734</t>
+          <t>106968; 156398</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97702; 142580</t>
+          <t>99319; 143874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215175; 309745</t>
+          <t>214747; 311928</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>198422; 260679</t>
+          <t>199560; 258014</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>313531; 388151</t>
+          <t>316576; 388206</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>310099; 386289</t>
+          <t>312428; 390815</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>585192; 1319657</t>
+          <t>584704; 1318188</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>306644; 378429</t>
+          <t>303891; 374096</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>436314; 523549</t>
+          <t>438667; 522074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>420266; 508712</t>
+          <t>422978; 509744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>832624; 1690428</t>
+          <t>840275; 1625930</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_5-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,88</t>
+          <t>1,51; 3,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,45</t>
+          <t>2,59; 5,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,03</t>
+          <t>2,85; 5,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,69</t>
+          <t>7,95; 12,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,33</t>
+          <t>2,49; 5,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 12,34</t>
+          <t>7,31; 12,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,57</t>
+          <t>8,69; 13,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 19,33</t>
+          <t>15,72; 19,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,24</t>
+          <t>2,33; 4,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,2</t>
+          <t>5,53; 8,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,24</t>
+          <t>6,25; 9,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 15,5</t>
+          <t>12,62; 15,52</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,09</t>
+          <t>2,55; 5,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,05</t>
+          <t>2,67; 4,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,23</t>
+          <t>2,19; 4,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,87</t>
+          <t>6,71; 9,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,61</t>
+          <t>4,58; 7,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 11,12</t>
+          <t>7,34; 10,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,11</t>
+          <t>7,06; 10,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,12; 17,65</t>
+          <t>13,71; 17,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,87</t>
+          <t>3,86; 5,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,57</t>
+          <t>5,43; 7,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,25</t>
+          <t>5,03; 7,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 12,43</t>
+          <t>10,62; 13,05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,39</t>
+          <t>2,31; 5,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,68</t>
+          <t>2,54; 5,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,8</t>
+          <t>2,23; 4,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,56</t>
+          <t>5,71; 9,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 12,51</t>
+          <t>8,02; 12,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,56</t>
+          <t>7,37; 11,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,64</t>
+          <t>6,63; 10,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 65,55</t>
+          <t>12,47; 16,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,36</t>
+          <t>5,48; 8,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,26</t>
+          <t>5,46; 8,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,31</t>
+          <t>4,8; 7,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,37; 46,83</t>
+          <t>9,72; 12,57</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,87</t>
+          <t>2,83; 5,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,46</t>
+          <t>2,64; 5,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,18</t>
+          <t>2,57; 4,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,24</t>
+          <t>6,85; 10,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,84</t>
+          <t>5,61; 8,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,35</t>
+          <t>9,12; 13,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,26</t>
+          <t>8,98; 13,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 19,58</t>
+          <t>15,9; 19,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,54</t>
+          <t>4,54; 6,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,1</t>
+          <t>6,59; 8,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,85</t>
+          <t>6,29; 8,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 14,45</t>
+          <t>11,96; 14,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,15</t>
+          <t>2,82; 4,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,56</t>
+          <t>3,13; 4,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,24</t>
+          <t>2,88; 4,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,02</t>
+          <t>7,62; 9,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,64</t>
+          <t>5,89; 7,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 10,91</t>
+          <t>8,94; 11,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 11,03</t>
+          <t>8,71; 10,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,75; 35,51</t>
+          <t>15,45; 17,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,62</t>
+          <t>4,56; 5,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 7,47</t>
+          <t>6,29; 7,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,35</t>
+          <t>6,13; 7,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,72; 22,67</t>
+          <t>11,87; 13,22</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65554</t>
+          <t>69391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>122230</t>
+          <t>129978</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>187784</t>
+          <t>199370</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10983; 26949</t>
+          <t>10491; 26614</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18258; 38315</t>
+          <t>18236; 41186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19196; 40670</t>
+          <t>19233; 39787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52785; 80637</t>
+          <t>54880; 84807</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17633; 36692</t>
+          <t>17160; 36817</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51632; 85982</t>
+          <t>50988; 84927</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58928; 91318</t>
+          <t>58466; 91178</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>98488; 140201</t>
+          <t>115394; 146436</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31384; 58582</t>
+          <t>32165; 57736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77501; 114848</t>
+          <t>77488; 114326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85235; 124531</t>
+          <t>84184; 125813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>165495; 210951</t>
+          <t>179805; 221108</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>85174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>151707</t>
+          <t>165449</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>229999</t>
+          <t>250622</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25195; 48915</t>
+          <t>24524; 48657</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26110; 51383</t>
+          <t>27206; 50789</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21685; 43225</t>
+          <t>22403; 44581</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37347; 105847</t>
+          <t>70393; 101809</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42426; 73661</t>
+          <t>44340; 73463</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76542; 114765</t>
+          <t>75762; 113447</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74995; 115818</t>
+          <t>73627; 113429</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>135388; 169226</t>
+          <t>146889; 183812</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75930; 113362</t>
+          <t>74426; 112331</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109465; 155108</t>
+          <t>111404; 157166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102365; 149835</t>
+          <t>103945; 149867</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>154073; 267467</t>
+          <t>225183; 276813</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52773</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>308198</t>
+          <t>119213</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>360971</t>
+          <t>178456</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14982; 36601</t>
+          <t>15698; 35479</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18971; 43022</t>
+          <t>19211; 41963</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17344; 36431</t>
+          <t>16939; 36528</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40740; 67381</t>
+          <t>45872; 75124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55895; 85542</t>
+          <t>54872; 86882</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56906; 89810</t>
+          <t>57244; 89176</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51914; 83534</t>
+          <t>52065; 86004</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>125105; 611821</t>
+          <t>101281; 135069</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76927; 113882</t>
+          <t>74710; 113605</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83503; 126730</t>
+          <t>83758; 123672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73284; 112933</t>
+          <t>74153; 113216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>169896; 767159</t>
+          <t>156988; 203074</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78618</t>
+          <t>82803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>186173</t>
+          <t>197766</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>264791</t>
+          <t>280569</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24716; 45853</t>
+          <t>26630; 47833</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25217; 51777</t>
+          <t>25027; 51882</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24294; 48612</t>
+          <t>24125; 46430</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64008; 94888</t>
+          <t>67775; 99148</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58436; 91814</t>
+          <t>58295; 91938</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97041; 140464</t>
+          <t>95900; 137412</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93884; 138405</t>
+          <t>93740; 136921</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>151024; 214421</t>
+          <t>177945; 220518</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91772; 129530</t>
+          <t>90000; 130460</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132547; 181960</t>
+          <t>131725; 179867</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124403; 175382</t>
+          <t>124618; 173035</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>225749; 292210</t>
+          <t>252216; 307652</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>275237</t>
+          <t>296611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>768308</t>
+          <t>612406</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1043545</t>
+          <t>909017</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94626; 136121</t>
+          <t>92334; 132324</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>106968; 156398</t>
+          <t>107358; 155302</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99319; 143874</t>
+          <t>97806; 141994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214747; 311928</t>
+          <t>269188; 326031</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>199560; 258014</t>
+          <t>198888; 259829</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>316576; 388206</t>
+          <t>318098; 393390</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>312428; 390815</t>
+          <t>308721; 386225</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>584704; 1318188</t>
+          <t>577420; 648180</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>303891; 374096</t>
+          <t>303623; 375812</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>438667; 522074</t>
+          <t>439319; 528206</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>422978; 509744</t>
+          <t>425038; 509279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>840275; 1625930</t>
+          <t>863262; 960896</t>
         </is>
       </c>
     </row>
